--- a/accident_report.xlsx
+++ b/accident_report.xlsx
@@ -661,7 +661,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2.08 seconds</t>
+          <t>2.64 seconds</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -675,11 +675,11 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1316</v>
+        <v>1297</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -688,11 +688,11 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1451</v>
+        <v>1493</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>-80.8</t>
+          <t>-73.0</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr"/>
@@ -717,12 +717,12 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>3213773.80</t>
+          <t>2547317.09</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -740,11 +740,11 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>- Solar-powered lighting solutions
+          <t>- Install median barriers
 - Public awareness campaigns on drinking and driving
-- Install anti-skid road surfaces
-- One-way traffic in narrow roads
-- Install breathalyzer devices</t>
+- Solar-powered lighting solutions
+- Weather-based speed limit adjustments
+- Stricter DUI checkpoints</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>85.3% of historical accidents in Main Highway share severe severity.</t>
+          <t>85.7% of historical accidents in Main Highway share severe severity.</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -774,17 +774,17 @@
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>3213773.80</t>
+          <t>2547317.09</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>2607714.87</t>
+          <t>2090035.85</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>18.86%</t>
+          <t>17.95%</t>
         </is>
       </c>
       <c r="AE4" s="3" t="inlineStr">

--- a/accident_report.xlsx
+++ b/accident_report.xlsx
@@ -441,7 +441,7 @@
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
@@ -651,7 +651,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Head-on collision</t>
+          <t>Vehicle-pedestrian collision</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2.64 seconds</t>
+          <t>1.68 seconds</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Drunk Driving</t>
+          <t>Mechanical Failure</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -675,28 +675,24 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1297</v>
+        <v>1249</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Car 2</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>1493</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>-73.0</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Pedestrian</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>77</v>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
           <t>wet</t>
@@ -713,16 +709,16 @@
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2547317.09</t>
+          <t>179950.02</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -740,21 +736,21 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>- Install median barriers
-- Public awareness campaigns on drinking and driving
-- Solar-powered lighting solutions
-- Weather-based speed limit adjustments
-- Stricter DUI checkpoints</t>
+          <t>- Solar-powered lighting solutions
+- Improve maintenance education
+- Improve drainage systems
+- Install pedestrian crossings
+- Mandatory vehicle inspections</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>Driver state (Under influence) affected reaction time (Impaired decision making due to alcohol or substances.); Road geometry (straight) with wet surface influenced braking distance; Limited lighting stretched driver perception; Primary cause flagged: Drunk Driving; Interventions tested: speed checkpoint, driver safety campaign, improved street lighting, road surface treatment.</t>
+          <t>Driver state (Under influence) affected reaction time (Impaired decision making due to alcohol or substances.); Road geometry (straight) with wet surface influenced braking distance; Limited lighting stretched driver perception; Primary cause flagged: Mechanical Failure; Interventions tested: speed checkpoint, driver safety campaign, improved street lighting, road surface treatment.</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>85.7% of historical accidents in Main Highway share severe severity.</t>
+          <t>87.2% of historical accidents in Main Highway share severe severity.</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -769,22 +765,22 @@
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>2547317.09</t>
+          <t>179950.02</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>2090035.85</t>
+          <t>134962.52</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>17.95%</t>
+          <t>25.00%</t>
         </is>
       </c>
       <c r="AE4" s="3" t="inlineStr">

--- a/accident_report.xlsx
+++ b/accident_report.xlsx
@@ -651,7 +651,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Vehicle-pedestrian collision</t>
+          <t>Head-on collision</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>1.68 seconds</t>
+          <t>2.86 seconds</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -675,24 +675,28 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1249</v>
+        <v>1218</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>81.3</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Pedestrian</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>77</v>
-      </c>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Car 2</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>1241</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>-57.1</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr">
         <is>
           <t>wet</t>
@@ -709,16 +713,16 @@
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>179950.02</t>
+          <t>2082317.08</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -736,21 +740,21 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>- Solar-powered lighting solutions
-- Improve maintenance education
-- Improve drainage systems
-- Install pedestrian crossings
+          <t>- Weather-based speed limit adjustments
+- Upgrade to LED lighting systems
+- Create emergency roadside assistance programs
+- One-way traffic in narrow roads
 - Mandatory vehicle inspections</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>Driver state (Under influence) affected reaction time (Impaired decision making due to alcohol or substances.); Road geometry (straight) with wet surface influenced braking distance; Limited lighting stretched driver perception; Primary cause flagged: Mechanical Failure; Interventions tested: speed checkpoint, driver safety campaign, improved street lighting, road surface treatment.</t>
+          <t>Mechanical failure in vehicle systems interacts with human response capabilities and road conditions, creating unexpected hazards in systems theory.</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>87.2% of historical accidents in Main Highway share severe severity.</t>
+          <t>88.1% of historical accidents in Main Highway share severe severity.</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -765,22 +769,22 @@
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>179950.02</t>
+          <t>2082317.08</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>134962.52</t>
+          <t>1685958.92</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>25.00%</t>
+          <t>19.03%</t>
         </is>
       </c>
       <c r="AE4" s="3" t="inlineStr">

--- a/accident_report.xlsx
+++ b/accident_report.xlsx
@@ -441,7 +441,7 @@
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
@@ -651,7 +651,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Head-on collision</t>
+          <t>Rear-end collision</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2.86 seconds</t>
+          <t>10.01 seconds</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Mechanical Failure</t>
+          <t>Poor Visibility</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -675,11 +675,11 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1218</v>
+        <v>1275</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -688,11 +688,11 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1241</v>
+        <v>1412</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>-57.1</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr"/>
@@ -713,25 +713,25 @@
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2082317.08</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>none</t>
         </is>
       </c>
       <c r="T4" s="3" t="n">
-        <v>10</v>
+        <v>2.1</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
@@ -740,21 +740,21 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>- Weather-based speed limit adjustments
-- Upgrade to LED lighting systems
-- Create emergency roadside assistance programs
-- One-way traffic in narrow roads
-- Mandatory vehicle inspections</t>
+          <t>- Solar-powered lighting solutions
+- Improve weather-responsive lighting systems
+- Increase following distance education
+- Weather-based speed limit adjustments
+- Upgrade street lighting</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>Mechanical failure in vehicle systems interacts with human response capabilities and road conditions, creating unexpected hazards in systems theory.</t>
+          <t>Poor visibility limits human perception, interacting with vehicle lighting and road markings in systems theory to compromise safety margins.</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>88.1% of historical accidents in Main Highway share severe severity.</t>
+          <t>0.0% of historical accidents in Main Highway share none severity.</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -764,42 +764,42 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>2082317.08</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>1685958.92</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>19.03%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>0.00 (Baseline 10.00, Intervention 10.00)</t>
+          <t>1.97 (Baseline 2.10, Intervention 0.13)</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AG4" s="3" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>0.13</t>
         </is>
       </c>
     </row>

--- a/accident_report.xlsx
+++ b/accident_report.xlsx
@@ -441,7 +441,7 @@
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
@@ -651,7 +651,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Rear-end collision</t>
+          <t>Head-on collision</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>10.01 seconds</t>
+          <t>2.26 seconds</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Poor Visibility</t>
+          <t>Drunk Driving</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -675,11 +675,11 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1275</v>
+        <v>1356</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -688,11 +688,11 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1412</v>
+        <v>1313</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>-68.7</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr"/>
@@ -713,25 +713,25 @@
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2850409.54</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="T4" s="3" t="n">
-        <v>2.1</v>
+        <v>10</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
@@ -741,20 +741,20 @@
       <c r="V4" s="3" t="inlineStr">
         <is>
           <t>- Solar-powered lighting solutions
-- Improve weather-responsive lighting systems
-- Increase following distance education
 - Weather-based speed limit adjustments
-- Upgrade street lighting</t>
+- Stricter DUI checkpoints
+- Improve lane markings
+- Public awareness campaigns on drinking and driving</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>Poor visibility limits human perception, interacting with vehicle lighting and road markings in systems theory to compromise safety margins.</t>
+          <t>Drunk driving impairs human judgment and reaction time, interacting with vehicle control systems and road geometry to create hazardous situations in systems theory.</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>0.0% of historical accidents in Main Highway share none severity.</t>
+          <t>88.1% of historical accidents in Main Highway share severe severity.</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -764,42 +764,42 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2850409.54</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2300233.04</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>19.30%</t>
         </is>
       </c>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>1.97 (Baseline 2.10, Intervention 0.13)</t>
+          <t>0.00 (Baseline 10.00, Intervention 10.00)</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AG4" s="3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>10.00</t>
         </is>
       </c>
     </row>

--- a/accident_report.xlsx
+++ b/accident_report.xlsx
@@ -441,7 +441,7 @@
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
@@ -651,22 +651,22 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Head-on collision</t>
+          <t>Rear-end collision</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Main Highway, Labo, Camarines Norte</t>
+          <t>Bayabas, Labo, Camarines Norte</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2.26 seconds</t>
+          <t>10.01 seconds</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Drunk Driving</t>
+          <t>Overspeeding</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -675,11 +675,11 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1356</v>
+        <v>1447</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -688,50 +688,50 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1313</v>
+        <v>1492</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>-68.7</t>
+          <t>105.9</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>wet</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>good</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Rainy</t>
+          <t>Sunny</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2850409.54</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>none</t>
         </is>
       </c>
       <c r="T4" s="3" t="n">
-        <v>10</v>
+        <v>0.95</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
@@ -740,66 +740,66 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>- Solar-powered lighting solutions
-- Weather-based speed limit adjustments
-- Stricter DUI checkpoints
-- Improve lane markings
-- Public awareness campaigns on drinking and driving</t>
+          <t>- Regular road maintenance
+- Implement speed cameras
+- Maintain current lighting standards
+- Add speed bumps in high-risk areas
+- Install rear-end collision warning systems</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>Drunk driving impairs human judgment and reaction time, interacting with vehicle control systems and road geometry to create hazardous situations in systems theory.</t>
+          <t>Overspeeding amplifies the impact of poor road conditions and reduces reaction time, leading to severe collisions in systems theory where human factors interact with vehicle dynamics and environmental constraints.</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>88.1% of historical accidents in Main Highway share severe severity.</t>
+          <t>Historical validation unavailable.</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>Speed Checkpoint, Driver Safety Campaign, Improved Street Lighting, Road Surface Treatment</t>
+          <t>Road Surface Treatment, Improved Street Lighting, Speed Checkpoint</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>2850409.54</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>2300233.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>19.30%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>0.00 (Baseline 10.00, Intervention 10.00)</t>
+          <t>0.00 (Baseline 0.95, Intervention 0.95)</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AG4" s="3" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>0.95</t>
         </is>
       </c>
     </row>

--- a/accident_report.xlsx
+++ b/accident_report.xlsx
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1447</v>
+        <v>1249</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -688,11 +688,11 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1492</v>
+        <v>1468</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>105.9</t>
+          <t>121.4</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr"/>
@@ -741,10 +741,10 @@
       <c r="V4" s="3" t="inlineStr">
         <is>
           <t>- Regular road maintenance
+- Increase speed limit enforcement
+- Increase following distance education
 - Implement speed cameras
-- Maintain current lighting standards
-- Add speed bumps in high-risk areas
-- Install rear-end collision warning systems</t>
+- Maintain current lighting standards</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">

--- a/accident_report.xlsx
+++ b/accident_report.xlsx
@@ -441,7 +441,7 @@
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
@@ -651,22 +651,22 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Rear-end collision</t>
+          <t>Side-impact (T-bone) collision</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Bayabas, Labo, Camarines Norte</t>
+          <t>Main Highway, Labo, Camarines Norte</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>10.01 seconds</t>
+          <t>2.24 seconds</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Overspeeding</t>
+          <t>Drunk Driving</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -675,11 +675,11 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1249</v>
+        <v>1274</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -688,50 +688,46 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1468</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>121.4</t>
-        </is>
-      </c>
+        <v>1305</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="3" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>dry</t>
+          <t>wet</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Sunny</t>
+          <t>Rainy</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1672226.88</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="T4" s="3" t="n">
-        <v>0.95</v>
+        <v>10</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
@@ -740,66 +736,66 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>- Regular road maintenance
-- Increase speed limit enforcement
-- Increase following distance education
-- Implement speed cameras
-- Maintain current lighting standards</t>
+          <t>- Improve drainage systems
+- Stricter DUI checkpoints
+- Public awareness campaigns on drinking and driving
+- Enhanced crosswalk protections
+- Upgrade to LED lighting systems</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>Overspeeding amplifies the impact of poor road conditions and reduces reaction time, leading to severe collisions in systems theory where human factors interact with vehicle dynamics and environmental constraints.</t>
+          <t>Drunk driving impairs human judgment and reaction time, interacting with vehicle control systems and road geometry to create hazardous situations in systems theory.</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>Historical validation unavailable.</t>
+          <t>88.9% of historical accidents in Main Highway share severe severity.</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>Road Surface Treatment, Improved Street Lighting, Speed Checkpoint</t>
+          <t>Speed Checkpoint, Driver Safety Campaign, Improved Street Lighting, Road Surface Treatment</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1672226.88</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1254047.54</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25.01%</t>
         </is>
       </c>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>0.00 (Baseline 0.95, Intervention 0.95)</t>
+          <t>0.00 (Baseline 10.00, Intervention 10.00)</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AG4" s="3" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>10.00</t>
         </is>
       </c>
     </row>

--- a/accident_report.xlsx
+++ b/accident_report.xlsx
@@ -441,7 +441,7 @@
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
@@ -651,22 +651,22 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Side-impact (T-bone) collision</t>
+          <t>Rear-end collision</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Main Highway, Labo, Camarines Norte</t>
+          <t>Bayabas, Labo, Camarines Norte</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2.24 seconds</t>
+          <t>10.01 seconds</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Drunk Driving</t>
+          <t>Overspeeding</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -675,11 +675,11 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1274</v>
+        <v>1308</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -688,46 +688,50 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1305</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr"/>
+        <v>1428</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>71.3</t>
+        </is>
+      </c>
       <c r="K4" s="3" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>wet</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>good</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Rainy</t>
+          <t>Sunny</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>1672226.88</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>none</t>
         </is>
       </c>
       <c r="T4" s="3" t="n">
-        <v>10</v>
+        <v>0.95</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
@@ -736,66 +740,66 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>- Improve drainage systems
-- Stricter DUI checkpoints
-- Public awareness campaigns on drinking and driving
-- Enhanced crosswalk protections
-- Upgrade to LED lighting systems</t>
+          <t>- Add speed bumps in high-risk areas
+- Regular road maintenance
+- Increase following distance education
+- Increase speed limit enforcement
+- Maintain current lighting standards</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>Drunk driving impairs human judgment and reaction time, interacting with vehicle control systems and road geometry to create hazardous situations in systems theory.</t>
+          <t>Overspeeding amplifies the impact of poor road conditions and reduces reaction time, leading to severe collisions in systems theory where human factors interact with vehicle dynamics and environmental constraints.</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>88.9% of historical accidents in Main Highway share severe severity.</t>
+          <t>Historical validation unavailable.</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>Speed Checkpoint, Driver Safety Campaign, Improved Street Lighting, Road Surface Treatment</t>
+          <t>Road Surface Treatment, Improved Street Lighting, Speed Checkpoint</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>1672226.88</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>1254047.54</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>25.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>0.00 (Baseline 10.00, Intervention 10.00)</t>
+          <t>0.00 (Baseline 0.95, Intervention 0.95)</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AG4" s="3" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>0.95</t>
         </is>
       </c>
     </row>

--- a/accident_report.xlsx
+++ b/accident_report.xlsx
@@ -441,7 +441,7 @@
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
@@ -651,22 +651,22 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Rear-end collision</t>
+          <t>Side-impact (T-bone) collision</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Bayabas, Labo, Camarines Norte</t>
+          <t>Malaya, Labo, Camarines Norte</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>10.01 seconds</t>
+          <t>2.53 seconds</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Overspeeding</t>
+          <t>Drunk Driving</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -675,11 +675,11 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1308</v>
+        <v>1375</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -688,50 +688,46 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1428</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>71.3</t>
-        </is>
-      </c>
+        <v>1351</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="3" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>dry</t>
+          <t>wet</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Sunny</t>
+          <t>Rainy</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1538462.92</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="T4" s="3" t="n">
-        <v>0.95</v>
+        <v>10</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
@@ -740,66 +736,66 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>- Add speed bumps in high-risk areas
-- Regular road maintenance
-- Increase following distance education
-- Increase speed limit enforcement
-- Maintain current lighting standards</t>
+          <t>- Improve drainage systems
+- Stricter DUI checkpoints
+- Install turning signal cameras
+- Install additional street lights
+- Public awareness campaigns on drinking and driving</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>Overspeeding amplifies the impact of poor road conditions and reduces reaction time, leading to severe collisions in systems theory where human factors interact with vehicle dynamics and environmental constraints.</t>
+          <t>Drunk driving impairs human judgment and reaction time, interacting with vehicle control systems and road geometry to create hazardous situations in systems theory.</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>Historical validation unavailable.</t>
+          <t>No recorded accidents in Malaya for validation.</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>Road Surface Treatment, Improved Street Lighting, Speed Checkpoint</t>
+          <t>Improved Street Lighting, Road Surface Treatment, Speed Checkpoint</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1538462.92</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1153704.16</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25.01%</t>
         </is>
       </c>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>0.00 (Baseline 0.95, Intervention 0.95)</t>
+          <t>0.00 (Baseline 10.00, Intervention 10.00)</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AG4" s="3" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>10.00</t>
         </is>
       </c>
     </row>

--- a/accident_report.xlsx
+++ b/accident_report.xlsx
@@ -651,17 +651,17 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Side-impact (T-bone) collision</t>
+          <t>Rear-end collision</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Malaya, Labo, Camarines Norte</t>
+          <t>Main Highway, Labo, Camarines Norte</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2.53 seconds</t>
+          <t>10.01 seconds</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -675,11 +675,11 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1375</v>
+        <v>1362</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -688,46 +688,50 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1351</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr"/>
+        <v>1343</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>93.6</t>
+        </is>
+      </c>
       <c r="K4" s="3" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>wet</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>good</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Rainy</t>
+          <t>Sunny</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>1538462.92</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>none</t>
         </is>
       </c>
       <c r="T4" s="3" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
@@ -736,11 +740,11 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>- Improve drainage systems
-- Stricter DUI checkpoints
-- Install turning signal cameras
-- Install additional street lights
-- Public awareness campaigns on drinking and driving</t>
+          <t>- Stricter DUI checkpoints
+- Regular road maintenance
+- Install breathalyzer devices
+- Increase following distance education
+- Maintain current lighting standards</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
@@ -750,52 +754,52 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>No recorded accidents in Malaya for validation.</t>
+          <t>Historical validation unavailable.</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>Improved Street Lighting, Road Surface Treatment, Speed Checkpoint</t>
+          <t>Speed Checkpoint, Driver Safety Campaign</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>1538462.92</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>1153704.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>25.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>0.00 (Baseline 10.00, Intervention 10.00)</t>
+          <t>0.00 (Baseline 0.10, Intervention 0.10)</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AG4" s="3" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>0.10</t>
         </is>
       </c>
     </row>

--- a/accident_report.xlsx
+++ b/accident_report.xlsx
@@ -740,11 +740,11 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>- Stricter DUI checkpoints
-- Regular road maintenance
-- Install breathalyzer devices
+          <t>- Pothole repair programs
 - Increase following distance education
-- Maintain current lighting standards</t>
+- Maintain current lighting standards
+- Public awareness campaigns on drinking and driving
+- Install breathalyzer devices</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">

--- a/accident_report.xlsx
+++ b/accident_report.xlsx
@@ -441,7 +441,7 @@
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
@@ -462,7 +462,7 @@
     <col width="30" customWidth="1" min="22" max="22"/>
     <col width="30" customWidth="1" min="23" max="23"/>
     <col width="30" customWidth="1" min="24" max="24"/>
-    <col width="30" customWidth="1" min="25" max="25"/>
+    <col width="24" customWidth="1" min="25" max="25"/>
     <col width="19" customWidth="1" min="26" max="26"/>
     <col width="23" customWidth="1" min="27" max="27"/>
     <col width="27" customWidth="1" min="28" max="28"/>
@@ -651,22 +651,22 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Rear-end collision</t>
+          <t>Side-impact (T-bone) collision</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Main Highway, Labo, Camarines Norte</t>
+          <t>Santa Cruz, Labo, Camarines Norte</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>10.01 seconds</t>
+          <t>2.75 seconds</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Drunk Driving</t>
+          <t>Fatigue</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1362</v>
+        <v>1415</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -688,18 +688,14 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1343</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>93.6</t>
-        </is>
-      </c>
+        <v>1479</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="3" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>dry</t>
+          <t>wet</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -709,29 +705,29 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Sunny</t>
+          <t>Foggy</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1155982.60</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="T4" s="3" t="n">
-        <v>0.1</v>
+        <v>10</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
@@ -740,16 +736,16 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>- Pothole repair programs
-- Increase following distance education
+          <t>- Campaigns on driver fatigue awareness
 - Maintain current lighting standards
-- Public awareness campaigns on drinking and driving
-- Install breathalyzer devices</t>
+- Enhanced crosswalk protections
+- Regulate maximum driving hours
+- Weather-based speed limit adjustments</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>Drunk driving impairs human judgment and reaction time, interacting with vehicle control systems and road geometry to create hazardous situations in systems theory.</t>
+          <t>Driver fatigue reduces reaction time and decision-making, interacting with lighting conditions and road geometry in systems theory to increase accident risk.</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
@@ -759,27 +755,27 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>Speed Checkpoint, Driver Safety Campaign</t>
+          <t>Road Surface Treatment</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1155982.60</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1155982.60</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
@@ -789,17 +785,17 @@
       </c>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>0.00 (Baseline 0.10, Intervention 0.10)</t>
+          <t>0.00 (Baseline 10.00, Intervention 10.00)</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AG4" s="3" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>10.00</t>
         </is>
       </c>
     </row>

--- a/accident_report.xlsx
+++ b/accident_report.xlsx
@@ -441,7 +441,7 @@
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
@@ -462,7 +462,7 @@
     <col width="30" customWidth="1" min="22" max="22"/>
     <col width="30" customWidth="1" min="23" max="23"/>
     <col width="30" customWidth="1" min="24" max="24"/>
-    <col width="24" customWidth="1" min="25" max="25"/>
+    <col width="30" customWidth="1" min="25" max="25"/>
     <col width="19" customWidth="1" min="26" max="26"/>
     <col width="23" customWidth="1" min="27" max="27"/>
     <col width="27" customWidth="1" min="28" max="28"/>
@@ -651,22 +651,22 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Side-impact (T-bone) collision</t>
+          <t>Rear-end collision</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Santa Cruz, Labo, Camarines Norte</t>
+          <t>Main Highway, Labo, Camarines Norte</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2.75 seconds</t>
+          <t>10.01 seconds</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Fatigue</t>
+          <t>Drunk Driving</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1415</v>
+        <v>1362</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -688,14 +688,18 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1479</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr"/>
+        <v>1343</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>93.6</t>
+        </is>
+      </c>
       <c r="K4" s="3" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>wet</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -705,29 +709,29 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Foggy</t>
+          <t>Sunny</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>1155982.60</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>none</t>
         </is>
       </c>
       <c r="T4" s="3" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
@@ -736,16 +740,16 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>- Campaigns on driver fatigue awareness
-- Maintain current lighting standards
-- Enhanced crosswalk protections
-- Regulate maximum driving hours
-- Weather-based speed limit adjustments</t>
+          <t>- Regular road maintenance
+- Stricter DUI checkpoints
+- Install rear-end collision warning systems
+- Install breathalyzer devices
+- Maintain current lighting standards</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>Driver fatigue reduces reaction time and decision-making, interacting with lighting conditions and road geometry in systems theory to increase accident risk.</t>
+          <t>Drunk driving impairs human judgment and reaction time, interacting with vehicle control systems and road geometry to create hazardous situations in systems theory.</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
@@ -755,27 +759,27 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>Road Surface Treatment</t>
+          <t>Speed Checkpoint, Driver Safety Campaign</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>1155982.60</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>1155982.60</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
@@ -785,17 +789,17 @@
       </c>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>0.00 (Baseline 10.00, Intervention 10.00)</t>
+          <t>0.00 (Baseline 0.10, Intervention 0.10)</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AG4" s="3" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>0.10</t>
         </is>
       </c>
     </row>

--- a/accident_report.xlsx
+++ b/accident_report.xlsx
@@ -740,10 +740,10 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>- Regular road maintenance
+          <t>- Install breathalyzer devices
+- Install rear-end collision warning systems
+- Pothole repair programs
 - Stricter DUI checkpoints
-- Install rear-end collision warning systems
-- Install breathalyzer devices
 - Maintain current lighting standards</t>
         </is>
       </c>

--- a/accident_report.xlsx
+++ b/accident_report.xlsx
@@ -441,7 +441,7 @@
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
@@ -463,12 +463,12 @@
     <col width="30" customWidth="1" min="23" max="23"/>
     <col width="30" customWidth="1" min="24" max="24"/>
     <col width="30" customWidth="1" min="25" max="25"/>
-    <col width="19" customWidth="1" min="26" max="26"/>
-    <col width="23" customWidth="1" min="27" max="27"/>
+    <col width="30" customWidth="1" min="26" max="26"/>
+    <col width="30" customWidth="1" min="27" max="27"/>
     <col width="27" customWidth="1" min="28" max="28"/>
     <col width="30" customWidth="1" min="29" max="29"/>
     <col width="28" customWidth="1" min="30" max="30"/>
-    <col width="30" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="31" max="31"/>
     <col width="21" customWidth="1" min="32" max="32"/>
     <col width="25" customWidth="1" min="33" max="33"/>
   </cols>
@@ -651,22 +651,22 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Rear-end collision</t>
+          <t>Head-on collision</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Main Highway, Labo, Camarines Norte</t>
+          <t>Bayabas, Labo, Camarines Norte</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>10.01 seconds</t>
+          <t>2.94 seconds</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Drunk Driving</t>
+          <t>Reckless Driving</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1362</v>
+        <v>1345</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -688,18 +688,18 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1343</v>
+        <v>1302</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>-59.0</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>dry</t>
+          <t>wet</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -709,29 +709,29 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Sunny</t>
+          <t>Rainy</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2727601.89</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="T4" s="3" t="n">
-        <v>0.1</v>
+        <v>10</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
@@ -740,16 +740,16 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>- Install breathalyzer devices
-- Install rear-end collision warning systems
-- Pothole repair programs
-- Stricter DUI checkpoints
-- Maintain current lighting standards</t>
+          <t>- Maintain current lighting standards
+- Improve lane markings
+- Increase traffic police presence
+- Enhanced driver training programs
+- Weather-based speed limit adjustments</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>Drunk driving impairs human judgment and reaction time, interacting with vehicle control systems and road geometry to create hazardous situations in systems theory.</t>
+          <t>Reckless driving combines aggressive human behavior with vehicle capabilities and environmental factors in systems theory, leading to high-risk interactions.</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
@@ -759,47 +759,47 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>Speed Checkpoint, Driver Safety Campaign</t>
+          <t>Road Surface Treatment, Improved Street Lighting</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>severe: 11, none: 7, moderate: 2</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>severe: 10, none: 8, moderate: 2</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>978339.69</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>725787.50</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>0.00 (Baseline 0.10, Intervention 0.10)</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>7.18</t>
         </is>
       </c>
       <c r="AG4" s="3" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>

--- a/accident_report.xlsx
+++ b/accident_report.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG4"/>
+  <dimension ref="A1:AF4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -461,16 +461,15 @@
     <col width="30" customWidth="1" min="21" max="21"/>
     <col width="30" customWidth="1" min="22" max="22"/>
     <col width="30" customWidth="1" min="23" max="23"/>
-    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="24" customWidth="1" min="24" max="24"/>
     <col width="30" customWidth="1" min="25" max="25"/>
     <col width="30" customWidth="1" min="26" max="26"/>
-    <col width="30" customWidth="1" min="27" max="27"/>
-    <col width="27" customWidth="1" min="28" max="28"/>
-    <col width="30" customWidth="1" min="29" max="29"/>
-    <col width="28" customWidth="1" min="30" max="30"/>
-    <col width="19" customWidth="1" min="31" max="31"/>
-    <col width="21" customWidth="1" min="32" max="32"/>
-    <col width="25" customWidth="1" min="33" max="33"/>
+    <col width="27" customWidth="1" min="27" max="27"/>
+    <col width="30" customWidth="1" min="28" max="28"/>
+    <col width="28" customWidth="1" min="29" max="29"/>
+    <col width="19" customWidth="1" min="30" max="30"/>
+    <col width="21" customWidth="1" min="31" max="31"/>
+    <col width="25" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -599,50 +598,45 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>Historical Validation</t>
+          <t>Interventions Applied</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>Interventions Applied</t>
+          <t>Baseline Severity</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>Baseline Severity</t>
+          <t>Intervention Severity</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>Intervention Severity</t>
+          <t>Baseline Impact Force (N)</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>Baseline Impact Force (N)</t>
+          <t>Intervention Impact Force (N)</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>Intervention Impact Force (N)</t>
+          <t>Impact Force Reduction (%)</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>Impact Force Reduction (%)</t>
+          <t>Risk Score Change</t>
         </is>
       </c>
       <c r="AE3" s="2" t="inlineStr">
         <is>
-          <t>Risk Score Change</t>
+          <t>Baseline Risk Score</t>
         </is>
       </c>
       <c r="AF3" s="2" t="inlineStr">
-        <is>
-          <t>Baseline Risk Score</t>
-        </is>
-      </c>
-      <c r="AG3" s="2" t="inlineStr">
         <is>
           <t>Intervention Risk Score</t>
         </is>
@@ -651,17 +645,17 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Head-on collision</t>
+          <t>Vehicle-pedestrian collision</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Bayabas, Labo, Camarines Norte</t>
+          <t>Bulhao, Labo, Camarines Norte</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2.94 seconds</t>
+          <t>1.74 seconds</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -675,28 +669,24 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1345</v>
+        <v>1206</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Car 2</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>1302</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>-59.0</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Pedestrian</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>70</v>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
           <t>wet</t>
@@ -709,29 +699,29 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Rainy</t>
+          <t>Foggy</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2727601.89</t>
+          <t>130842.55</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="T4" s="3" t="n">
-        <v>10</v>
+        <v>8.57</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
@@ -741,10 +731,10 @@
       <c r="V4" s="3" t="inlineStr">
         <is>
           <t>- Maintain current lighting standards
-- Improve lane markings
+- Install anti-skid road surfaces
 - Increase traffic police presence
-- Enhanced driver training programs
-- Weather-based speed limit adjustments</t>
+- Install pedestrian crossings
+- Implement point-based license system</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
@@ -754,52 +744,47 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>Historical validation unavailable.</t>
+          <t>Road Surface Treatment</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>Road Surface Treatment, Improved Street Lighting</t>
+          <t>severe: 14, none: 4, moderate: 2</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>severe: 11, none: 7, moderate: 2</t>
+          <t>severe: 9, moderate: 6, none: 5</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>severe: 10, none: 8, moderate: 2</t>
+          <t>938230.12</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>978339.69</t>
+          <t>720528.06</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>725787.50</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>7.18</t>
-        </is>
-      </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t>6.00</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>

--- a/accident_report.xlsx
+++ b/accident_report.xlsx
@@ -441,7 +441,7 @@
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
@@ -461,9 +461,9 @@
     <col width="30" customWidth="1" min="21" max="21"/>
     <col width="30" customWidth="1" min="22" max="22"/>
     <col width="30" customWidth="1" min="23" max="23"/>
-    <col width="24" customWidth="1" min="24" max="24"/>
-    <col width="30" customWidth="1" min="25" max="25"/>
-    <col width="30" customWidth="1" min="26" max="26"/>
+    <col width="27" customWidth="1" min="24" max="24"/>
+    <col width="19" customWidth="1" min="25" max="25"/>
+    <col width="23" customWidth="1" min="26" max="26"/>
     <col width="27" customWidth="1" min="27" max="27"/>
     <col width="30" customWidth="1" min="28" max="28"/>
     <col width="28" customWidth="1" min="29" max="29"/>
@@ -645,22 +645,22 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Vehicle-pedestrian collision</t>
+          <t>Head-on collision</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Bulhao, Labo, Camarines Norte</t>
+          <t>Malasugui, Labo, Camarines Norte</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>1.74 seconds</t>
+          <t>3.35 seconds</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Reckless Driving</t>
+          <t>Fatigue</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -669,27 +669,31 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Pedestrian</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>70</v>
-      </c>
+          <t>49.0</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Car 2</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>1499</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>-55.4</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>wet</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -699,29 +703,29 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Foggy</t>
+          <t>Sunny</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>130842.55</t>
+          <t>1865020.57</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="T4" s="3" t="n">
-        <v>8.57</v>
+        <v>10</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
@@ -730,61 +734,61 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>- Maintain current lighting standards
-- Install anti-skid road surfaces
-- Increase traffic police presence
-- Install pedestrian crossings
-- Implement point-based license system</t>
+          <t>- Campaigns on driver fatigue awareness
+- Regular road maintenance
+- Improve lane markings
+- Regulate maximum driving hours
+- Maintain current lighting standards</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>Reckless driving combines aggressive human behavior with vehicle capabilities and environmental factors in systems theory, leading to high-risk interactions.</t>
+          <t>Driver fatigue reduces reaction time and decision-making, interacting with lighting conditions and road geometry in systems theory to increase accident risk.</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>Road Surface Treatment</t>
+          <t>No interventions applied.</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>severe: 14, none: 4, moderate: 2</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>severe: 9, moderate: 6, none: 5</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>938230.12</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>720528.06</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>

--- a/accident_report.xlsx
+++ b/accident_report.xlsx
@@ -441,7 +441,7 @@
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
@@ -461,7 +461,7 @@
     <col width="30" customWidth="1" min="21" max="21"/>
     <col width="30" customWidth="1" min="22" max="22"/>
     <col width="30" customWidth="1" min="23" max="23"/>
-    <col width="27" customWidth="1" min="24" max="24"/>
+    <col width="30" customWidth="1" min="24" max="24"/>
     <col width="19" customWidth="1" min="25" max="25"/>
     <col width="23" customWidth="1" min="26" max="26"/>
     <col width="27" customWidth="1" min="27" max="27"/>
@@ -645,22 +645,22 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Head-on collision</t>
+          <t>Vehicle-pedestrian collision</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Malasugui, Labo, Camarines Norte</t>
+          <t>San Antonio, Labo, Camarines Norte</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>3.35 seconds</t>
+          <t>2.54 seconds</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Fatigue</t>
+          <t>Overspeeding</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -669,31 +669,27 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1222</v>
+        <v>1488</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>49.0</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Car 2</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>1499</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>-55.4</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Pedestrian</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>66</v>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>dry</t>
+          <t>wet</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -703,29 +699,29 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Sunny</t>
+          <t>Rainy</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>1865020.57</t>
+          <t>117704.74</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="T4" s="3" t="n">
-        <v>10</v>
+        <v>8.48</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
@@ -734,21 +730,21 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>- Campaigns on driver fatigue awareness
-- Regular road maintenance
-- Improve lane markings
-- Regulate maximum driving hours
-- Maintain current lighting standards</t>
+          <t>- Install anti-skid road surfaces
+- Increase speed limit enforcement
+- Maintain current lighting standards
+- Pedestrian safety education
+- Add speed bumps in high-risk areas</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>Driver fatigue reduces reaction time and decision-making, interacting with lighting conditions and road geometry in systems theory to increase accident risk.</t>
+          <t>Overspeeding amplifies the impact of poor road conditions and reduces reaction time, leading to severe collisions in systems theory where human factors interact with vehicle dynamics and environmental constraints.</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>No interventions applied.</t>
+          <t>Road Surface Treatment, Speed Checkpoint</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
